--- a/frontend/public/ejemplos/planificacion_nia/RQ-004_carta_control_interno.xlsx
+++ b/frontend/public/ejemplos/planificacion_nia/RQ-004_carta_control_interno.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,11 @@
           <t>Respuesta de auditoría</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>¿Se probará la eficacia del control? (Sí/No)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +505,7 @@
           <t>Revisar las notas de crédito de enero y su aprobación; prueba de corte de la última semana de diciembre.</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -542,6 +548,7 @@
           <t>Observar la toma física al cierre y conciliar el kárdex con la contabilidad.</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -584,6 +591,7 @@
           <t>Recalcular la pérdida crediticia esperada con la antigüedad de la cartera (NIIF 9).</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -626,6 +634,11 @@
           <t>Obtener el estudio actuarial al cierre y evaluar la competencia del actuario (NIA 500 y 620).</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -668,6 +681,7 @@
           <t>Evaluar los controles generales de TI y ampliar las pruebas de asientos de diario.</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -690,11 +704,7 @@
           <t>Existencia</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>3</t>
@@ -702,6 +712,7 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
